--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q20_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000651632532202297</v>
+        <v>0.0002476428873705577</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000651632532202297</v>
+        <v>0.0002476428873705577</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004662109078435502</v>
+        <v>0.0002092711298059304</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006190485051139412</v>
+        <v>0.0002327887542004305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006190485051139412</v>
+        <v>0.0002327887542004305</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003992198150225528</v>
+        <v>0.0002001488483148281</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005896261665259379</v>
+        <v>0.0002198345815483241</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005896261665259379</v>
+        <v>0.0002198345815483241</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003403552286586049</v>
+        <v>0.000187275547970822</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0005844177435359748</v>
+        <v>0.0002176464828554491</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005844177435359748</v>
+        <v>0.0002176464828554491</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003003579381911184</v>
+        <v>0.0001747786159776142</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.000623788020450536</v>
+        <v>0.0002337429120470656</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000623788020450536</v>
+        <v>0.0002337429120470656</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003046763335757601</v>
+        <v>0.0001774757964154285</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0007203173877583454</v>
+        <v>0.0002725082270739187</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007203173877583454</v>
+        <v>0.0002725082270739187</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003592762506843078</v>
+        <v>0.0002049946256548418</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.000893767689938626</v>
+        <v>0.0003411239007093036</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000893767689938626</v>
+        <v>0.0003411239007093036</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004438960516422503</v>
+        <v>0.000254699940495211</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001133831745199264</v>
+        <v>0.0004351423241117147</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001133831745199264</v>
+        <v>0.0004351423241117147</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0005505204025209468</v>
+        <v>0.0003237277141262536</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001421187518259347</v>
+        <v>0.0005463737694246697</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001421187518259347</v>
+        <v>0.0005463737694246697</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000691493395824427</v>
+        <v>0.0004114037025020983</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001731247223460067</v>
+        <v>0.0006646989618412607</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001731247223460067</v>
+        <v>0.0006646989618412607</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000846186869365968</v>
+        <v>0.0005054159139100365</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002028685282519252</v>
+        <v>0.000776680952115331</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002028685282519252</v>
+        <v>0.000776680952115331</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0009490696574644753</v>
+        <v>0.0005754302775882348</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002348060312759336</v>
+        <v>0.000896871963428469</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002348060312759336</v>
+        <v>0.000896871963428469</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001058227593275281</v>
+        <v>0.0006405814466630907</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002732176438932447</v>
+        <v>0.001043137982889968</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002732176438932447</v>
+        <v>0.001043137982889968</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00124361489814196</v>
+        <v>0.0007313214420881645</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003162351606432865</v>
+        <v>0.001208664653634486</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003162351606432865</v>
+        <v>0.001208664653634486</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001469504680668693</v>
+        <v>0.0008438729758469176</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003580360421678076</v>
+        <v>0.001370394387040983</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003580360421678076</v>
+        <v>0.001370394387040983</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001674325204599345</v>
+        <v>0.0009562191780404482</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003922997311404064</v>
+        <v>0.001503347953478618</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003922997311404064</v>
+        <v>0.001503347953478618</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00182770707505501</v>
+        <v>0.001051335299072107</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.004217547317914178</v>
+        <v>0.001617283706595412</v>
       </c>
       <c r="C18" t="n">
-        <v>0.004217547317914178</v>
+        <v>0.001617283706595412</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001943398111987959</v>
+        <v>0.001130446065973823</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.004423429058543614</v>
+        <v>0.00169657419595271</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004423429058543614</v>
+        <v>0.00169657419595271</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002021030316174215</v>
+        <v>0.001187926516684427</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.004558086218771324</v>
+        <v>0.001747652302866154</v>
       </c>
       <c r="C20" t="n">
-        <v>0.004558086218771324</v>
+        <v>0.001747652302866154</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002072085301038078</v>
+        <v>0.001225109356623887</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.004609907530358445</v>
+        <v>0.001766319038684528</v>
       </c>
       <c r="C21" t="n">
-        <v>0.004609907530358445</v>
+        <v>0.001766319038684528</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002084125450112035</v>
+        <v>0.001240254200735241</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.004632308953711812</v>
+        <v>0.001773405309810729</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004632308953711812</v>
+        <v>0.001773405309810729</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002093397515569965</v>
+        <v>0.001246930535223708</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.004566585200387546</v>
+        <v>0.00174696022987861</v>
       </c>
       <c r="C23" t="n">
-        <v>0.004566585200387546</v>
+        <v>0.00174696022987861</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002065955771815533</v>
+        <v>0.00123095121651246</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.004489791162038584</v>
+        <v>0.001716678177643065</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004489791162038584</v>
+        <v>0.001716678177643065</v>
       </c>
       <c r="D24" t="n">
-        <v>0.002026298790190145</v>
+        <v>0.001208245675983321</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.004386596268971909</v>
+        <v>0.001677097699003504</v>
       </c>
       <c r="C25" t="n">
-        <v>0.004386596268971909</v>
+        <v>0.001677097699003504</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001974867226596367</v>
+        <v>0.001179009566076515</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.004266815179631634</v>
+        <v>0.001631678912939474</v>
       </c>
       <c r="C26" t="n">
-        <v>0.004266815179631634</v>
+        <v>0.001631678912939474</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001914953121262772</v>
+        <v>0.001145514767942696</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.004159368621466559</v>
+        <v>0.00159058997129117</v>
       </c>
       <c r="C27" t="n">
-        <v>0.004159368621466559</v>
+        <v>0.00159058997129117</v>
       </c>
       <c r="D27" t="n">
-        <v>0.001862826649823807</v>
+        <v>0.00111482821964717</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.003984168192566695</v>
+        <v>0.001524393952833738</v>
       </c>
       <c r="C28" t="n">
-        <v>0.003984168192566695</v>
+        <v>0.001524393952833738</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001798247701575873</v>
+        <v>0.001073181396877571</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.003873633398502493</v>
+        <v>0.001482415512764508</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003873633398502493</v>
+        <v>0.001482415512764508</v>
       </c>
       <c r="D29" t="n">
-        <v>0.001754316898538069</v>
+        <v>0.001043862223623075</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003820039215899683</v>
+        <v>0.001462693346365272</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003820039215899683</v>
+        <v>0.001462693346365272</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001708769706493743</v>
+        <v>0.00101552481516356</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.00374548346158881</v>
+        <v>0.001434476714126284</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00374548346158881</v>
+        <v>0.001434476714126284</v>
       </c>
       <c r="D31" t="n">
-        <v>0.001687152227169319</v>
+        <v>0.001004264888788412</v>
       </c>
     </row>
   </sheetData>
